--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-2026-09-29.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-2026-09-29.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/29 10:28:07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20779</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>160000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>160000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20779.22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20779</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20779.22</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.22</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-2026-09-29.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-2026-09-29.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/29 12:01:33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>140000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>18181.82</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/29 10:22:56</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>160000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>20779.22</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>CS_006</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>160000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>38961.04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20779</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.22</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18182.04</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-2026-09-29.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-2026-09-29.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38961.04</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>38961.04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>38960</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>18182.04</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.04</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-2026-09-29.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-2026-09-29.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -271,83 +271,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>38961.04</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>38960</t>
+          <t>38961.04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>59739</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.04</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-20777.96</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-2026-09-29.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-2026-09-29.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/29 12:28:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -271,12 +271,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 10:28:07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -286,7 +286,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -295,86 +295,59 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>09/29 10:28:07</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>20779</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>38961.04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>38961.04</t>
+          <t>38960</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>59739</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>-20777.96</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
